--- a/human_resources_surveys/006_sick_leave_donation_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/006_sick_leave_donation_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_support',_'value':_'strong_support'}</t>
+          <t>strongly_support</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'strongly_support', 'value': 'strong_support'}</t>
+          <t>strongly support</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_support',_'value':_'somewhat_support'}</t>
+          <t>somewhat_support</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat_support', 'value': 'somewhat_support'}</t>
+          <t>somewhat support</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'neutral', 'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_opposed',_'value':_'somewhat_opposed'}</t>
+          <t>somewhat_opposed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat_opposed', 'value': 'somewhat_opposed'}</t>
+          <t>somewhat opposed</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_opposed',_'value':_'strong_opposed'}</t>
+          <t>strongly_opposed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'strongly_opposed', 'value': 'strong_opposed'}</t>
+          <t>strongly opposed</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_transparency',_'value':_'lack_of_transparency'}</t>
+          <t>lack_of_transparency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'lack_of_transparency', 'value': 'lack_of_transparency'}</t>
+          <t>lack of transparency</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'unclear_policies',_'value':_'unclear_policies'}</t>
+          <t>unclear_policies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'unclear_policies', 'value': 'unclear_policies'}</t>
+          <t>unclear policies</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'unequal_access',_'value':_'unequal_access'}</t>
+          <t>unequal_access</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'unequal_access', 'value': 'unequal_access'}</t>
+          <t>unequal access</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
